--- a/Team-Data/2007-08/1-27-2007-08.xlsx
+++ b/Team-Data/2007-08/1-27-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,28 +728,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E2" t="n">
         <v>19</v>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G2" t="n">
-        <v>0.463</v>
+        <v>0.475</v>
       </c>
       <c r="H2" t="n">
         <v>48.6</v>
       </c>
       <c r="I2" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="J2" t="n">
         <v>78.09999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.444</v>
+        <v>0.442</v>
       </c>
       <c r="L2" t="n">
         <v>3.9</v>
@@ -691,49 +758,49 @@
         <v>12</v>
       </c>
       <c r="N2" t="n">
-        <v>0.323</v>
+        <v>0.326</v>
       </c>
       <c r="O2" t="n">
-        <v>21.8</v>
+        <v>22.1</v>
       </c>
       <c r="P2" t="n">
-        <v>28.3</v>
+        <v>28.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.769</v>
+        <v>0.771</v>
       </c>
       <c r="R2" t="n">
         <v>12</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>30.2</v>
       </c>
       <c r="T2" t="n">
-        <v>42</v>
+        <v>42.2</v>
       </c>
       <c r="U2" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="V2" t="n">
         <v>15.3</v>
       </c>
       <c r="W2" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>94.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="AC2" t="n">
         <v>-0.7</v>
@@ -754,13 +821,13 @@
         <v>3</v>
       </c>
       <c r="AI2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ2" t="n">
         <v>26</v>
       </c>
       <c r="AK2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL2" t="n">
         <v>29</v>
@@ -772,7 +839,7 @@
         <v>29</v>
       </c>
       <c r="AO2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AP2" t="n">
         <v>6</v>
@@ -781,19 +848,19 @@
         <v>8</v>
       </c>
       <c r="AR2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AT2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="n">
         <v>18</v>
       </c>
       <c r="AV2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW2" t="n">
         <v>7</v>
@@ -802,16 +869,16 @@
         <v>3</v>
       </c>
       <c r="AY2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AZ2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC2" t="n">
         <v>16</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E3" t="n">
         <v>34</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.829</v>
       </c>
       <c r="H3" t="n">
         <v>48.2</v>
@@ -861,10 +928,10 @@
         <v>35.4</v>
       </c>
       <c r="J3" t="n">
-        <v>75.2</v>
+        <v>75</v>
       </c>
       <c r="K3" t="n">
-        <v>0.471</v>
+        <v>0.472</v>
       </c>
       <c r="L3" t="n">
         <v>7.2</v>
@@ -876,52 +943,52 @@
         <v>0.374</v>
       </c>
       <c r="O3" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="P3" t="n">
-        <v>27.2</v>
+        <v>27.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.767</v>
+        <v>0.765</v>
       </c>
       <c r="R3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>31.4</v>
+        <v>31.6</v>
       </c>
       <c r="T3" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U3" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="V3" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W3" t="n">
         <v>8.9</v>
       </c>
       <c r="X3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AA3" t="n">
         <v>22.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>98.90000000000001</v>
+        <v>99</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.7</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -957,16 +1024,16 @@
         <v>8</v>
       </c>
       <c r="AP3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
         <v>26</v>
       </c>
       <c r="AS3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AT3" t="n">
         <v>20</v>
@@ -984,7 +1051,7 @@
         <v>22</v>
       </c>
       <c r="AY3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
         <v>17</v>
@@ -993,7 +1060,7 @@
         <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC3" t="n">
         <v>1</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -1103,16 +1170,16 @@
         <v>-3.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF4" t="n">
         <v>22</v>
       </c>
       <c r="AG4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH4" t="n">
         <v>4</v>
@@ -1133,10 +1200,10 @@
         <v>16</v>
       </c>
       <c r="AN4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP4" t="n">
         <v>16</v>
@@ -1151,19 +1218,19 @@
         <v>23</v>
       </c>
       <c r="AT4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU4" t="n">
         <v>14</v>
       </c>
       <c r="AV4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AW4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX4" t="n">
         <v>13</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>14</v>
       </c>
       <c r="AY4" t="n">
         <v>28</v>
@@ -1172,7 +1239,7 @@
         <v>25</v>
       </c>
       <c r="BA4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BB4" t="n">
         <v>21</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -1207,67 +1274,67 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E5" t="n">
         <v>17</v>
       </c>
       <c r="F5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G5" t="n">
-        <v>0.395</v>
+        <v>0.405</v>
       </c>
       <c r="H5" t="n">
         <v>48.5</v>
       </c>
       <c r="I5" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="J5" t="n">
-        <v>85.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.421</v>
+        <v>0.423</v>
       </c>
       <c r="L5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="M5" t="n">
         <v>16</v>
       </c>
       <c r="N5" t="n">
-        <v>0.339</v>
+        <v>0.341</v>
       </c>
       <c r="O5" t="n">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="P5" t="n">
-        <v>23.2</v>
+        <v>23.5</v>
       </c>
       <c r="Q5" t="n">
         <v>0.75</v>
       </c>
       <c r="R5" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="S5" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T5" t="n">
-        <v>43.7</v>
+        <v>43.5</v>
       </c>
       <c r="U5" t="n">
-        <v>21.3</v>
+        <v>21.6</v>
       </c>
       <c r="V5" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="W5" t="n">
         <v>7.5</v>
       </c>
       <c r="X5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
         <v>5.7</v>
@@ -1276,34 +1343,34 @@
         <v>21.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>94.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3.1</v>
+        <v>-2.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AE5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF5" t="n">
         <v>19</v>
       </c>
       <c r="AG5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI5" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
@@ -1312,19 +1379,19 @@
         <v>24</v>
       </c>
       <c r="AM5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP5" t="n">
         <v>21</v>
       </c>
-      <c r="AO5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>23</v>
-      </c>
       <c r="AQ5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR5" t="n">
         <v>1</v>
@@ -1336,13 +1403,13 @@
         <v>7</v>
       </c>
       <c r="AU5" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AV5" t="n">
         <v>10</v>
       </c>
       <c r="AW5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX5" t="n">
         <v>15</v>
@@ -1354,13 +1421,13 @@
         <v>14</v>
       </c>
       <c r="BA5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F6" t="n">
         <v>19</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.548</v>
       </c>
       <c r="H6" t="n">
         <v>48.8</v>
@@ -1416,16 +1483,16 @@
         <v>6.4</v>
       </c>
       <c r="M6" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.349</v>
+        <v>0.351</v>
       </c>
       <c r="O6" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="P6" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="Q6" t="n">
         <v>0.722</v>
@@ -1443,7 +1510,7 @@
         <v>19.5</v>
       </c>
       <c r="V6" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W6" t="n">
         <v>7.8</v>
@@ -1455,40 +1522,40 @@
         <v>4.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB6" t="n">
         <v>97.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="AD6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE6" t="n">
         <v>15</v>
       </c>
-      <c r="AE6" t="n">
-        <v>13</v>
-      </c>
       <c r="AF6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AH6" t="n">
         <v>1</v>
       </c>
       <c r="AI6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ6" t="n">
         <v>9</v>
       </c>
       <c r="AK6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL6" t="n">
         <v>14</v>
@@ -1506,7 +1573,7 @@
         <v>15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR6" t="n">
         <v>3</v>
@@ -1521,19 +1588,19 @@
         <v>26</v>
       </c>
       <c r="AV6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY6" t="n">
         <v>16</v>
       </c>
       <c r="AZ6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA6" t="n">
         <v>23</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -1571,22 +1638,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F7" t="n">
         <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>0.698</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
       </c>
       <c r="I7" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="J7" t="n">
         <v>78.2</v>
@@ -1595,61 +1662,61 @@
         <v>0.47</v>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M7" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.357</v>
+        <v>0.36</v>
       </c>
       <c r="O7" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="P7" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.822</v>
+        <v>0.821</v>
       </c>
       <c r="R7" t="n">
         <v>10.5</v>
       </c>
       <c r="S7" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="T7" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U7" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V7" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="W7" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="X7" t="n">
         <v>5.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Z7" t="n">
         <v>22</v>
       </c>
       <c r="AA7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="AB7" t="n">
-        <v>101.1</v>
+        <v>101.3</v>
       </c>
       <c r="AC7" t="n">
         <v>4.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AE7" t="n">
         <v>5</v>
@@ -1661,7 +1728,7 @@
         <v>5</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI7" t="n">
         <v>11</v>
@@ -1679,13 +1746,13 @@
         <v>20</v>
       </c>
       <c r="AN7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO7" t="n">
         <v>6</v>
       </c>
       <c r="AP7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ7" t="n">
         <v>1</v>
@@ -1694,10 +1761,10 @@
         <v>20</v>
       </c>
       <c r="AS7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AT7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU7" t="n">
         <v>22</v>
@@ -1715,10 +1782,10 @@
         <v>5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BB7" t="n">
         <v>9</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -1753,28 +1820,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E8" t="n">
         <v>26</v>
       </c>
       <c r="F8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G8" t="n">
-        <v>0.605</v>
+        <v>0.619</v>
       </c>
       <c r="H8" t="n">
         <v>48.2</v>
       </c>
       <c r="I8" t="n">
-        <v>38.4</v>
+        <v>38.6</v>
       </c>
       <c r="J8" t="n">
-        <v>85.09999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="K8" t="n">
-        <v>0.451</v>
+        <v>0.453</v>
       </c>
       <c r="L8" t="n">
         <v>6</v>
@@ -1783,64 +1850,64 @@
         <v>18.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0.332</v>
+        <v>0.329</v>
       </c>
       <c r="O8" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="P8" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.756</v>
+        <v>0.757</v>
       </c>
       <c r="R8" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S8" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="T8" t="n">
-        <v>45.3</v>
+        <v>45.5</v>
       </c>
       <c r="U8" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="V8" t="n">
         <v>15.7</v>
       </c>
       <c r="W8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="X8" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="Y8" t="n">
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA8" t="n">
         <v>24.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>106.4</v>
+        <v>106.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AE8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF8" t="n">
         <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH8" t="n">
         <v>19</v>
@@ -1849,19 +1916,19 @@
         <v>5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM8" t="n">
         <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1873,7 +1940,7 @@
         <v>14</v>
       </c>
       <c r="AR8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS8" t="n">
         <v>3</v>
@@ -1885,16 +1952,16 @@
         <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX8" t="n">
         <v>1</v>
       </c>
       <c r="AY8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ8" t="n">
         <v>15</v>
@@ -1906,7 +1973,7 @@
         <v>4</v>
       </c>
       <c r="BC8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -2013,16 +2080,16 @@
         <v>7.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
         <v>3</v>
       </c>
       <c r="AG9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH9" t="n">
         <v>27</v>
@@ -2040,7 +2107,7 @@
         <v>19</v>
       </c>
       <c r="AM9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN9" t="n">
         <v>10</v>
@@ -2058,7 +2125,7 @@
         <v>17</v>
       </c>
       <c r="AS9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT9" t="n">
         <v>25</v>
@@ -2070,10 +2137,10 @@
         <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY9" t="n">
         <v>1</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -2117,46 +2184,46 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F10" t="n">
         <v>18</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6</v>
+        <v>0.591</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="J10" t="n">
-        <v>88.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="K10" t="n">
         <v>0.453</v>
       </c>
       <c r="L10" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0.35</v>
+        <v>0.352</v>
       </c>
       <c r="O10" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="P10" t="n">
-        <v>25.8</v>
+        <v>25.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.747</v>
+        <v>0.748</v>
       </c>
       <c r="R10" t="n">
         <v>12.2</v>
@@ -2165,16 +2232,16 @@
         <v>30</v>
       </c>
       <c r="T10" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U10" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="V10" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="W10" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X10" t="n">
         <v>4.4</v>
@@ -2183,22 +2250,22 @@
         <v>5.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>109.2</v>
+        <v>109.3</v>
       </c>
       <c r="AC10" t="n">
         <v>1.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF10" t="n">
         <v>9</v>
@@ -2207,7 +2274,7 @@
         <v>10</v>
       </c>
       <c r="AH10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2228,7 +2295,7 @@
         <v>16</v>
       </c>
       <c r="AO10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP10" t="n">
         <v>12</v>
@@ -2237,25 +2304,25 @@
         <v>20</v>
       </c>
       <c r="AR10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU10" t="n">
         <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AY10" t="n">
         <v>19</v>
@@ -2264,7 +2331,7 @@
         <v>27</v>
       </c>
       <c r="BA10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB10" t="n">
         <v>2</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E11" t="n">
         <v>24</v>
       </c>
       <c r="F11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G11" t="n">
-        <v>0.545</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
@@ -2326,40 +2393,40 @@
         <v>6.6</v>
       </c>
       <c r="M11" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="N11" t="n">
         <v>0.334</v>
       </c>
       <c r="O11" t="n">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="P11" t="n">
         <v>22.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.727</v>
+        <v>0.732</v>
       </c>
       <c r="R11" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S11" t="n">
-        <v>31.4</v>
+        <v>31.6</v>
       </c>
       <c r="T11" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
       <c r="U11" t="n">
         <v>21</v>
       </c>
       <c r="V11" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W11" t="n">
         <v>7.7</v>
       </c>
       <c r="X11" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y11" t="n">
         <v>4.4</v>
@@ -2371,22 +2438,22 @@
         <v>20.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>95.3</v>
+        <v>95.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE11" t="n">
         <v>13</v>
       </c>
       <c r="AF11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH11" t="n">
         <v>22</v>
@@ -2398,10 +2465,10 @@
         <v>12</v>
       </c>
       <c r="AK11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM11" t="n">
         <v>8</v>
@@ -2413,7 +2480,7 @@
         <v>27</v>
       </c>
       <c r="AP11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ11" t="n">
         <v>22</v>
@@ -2422,7 +2489,7 @@
         <v>6</v>
       </c>
       <c r="AS11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT11" t="n">
         <v>6</v>
@@ -2431,7 +2498,7 @@
         <v>20</v>
       </c>
       <c r="AV11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW11" t="n">
         <v>12</v>
@@ -2440,7 +2507,7 @@
         <v>4</v>
       </c>
       <c r="AY11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ11" t="n">
         <v>6</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -2559,19 +2626,19 @@
         <v>-1.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
         <v>17</v>
       </c>
       <c r="AF12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AG12" t="n">
         <v>19</v>
       </c>
       <c r="AH12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI12" t="n">
         <v>6</v>
@@ -2580,7 +2647,7 @@
         <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL12" t="n">
         <v>4</v>
@@ -2589,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO12" t="n">
         <v>16</v>
@@ -2619,16 +2686,16 @@
         <v>11</v>
       </c>
       <c r="AX12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AZ12" t="n">
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB12" t="n">
         <v>7</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-4.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE13" t="n">
         <v>26</v>
@@ -2756,7 +2823,7 @@
         <v>17</v>
       </c>
       <c r="AI13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ13" t="n">
         <v>19</v>
@@ -2783,7 +2850,7 @@
         <v>7</v>
       </c>
       <c r="AR13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS13" t="n">
         <v>7</v>
@@ -2795,10 +2862,10 @@
         <v>15</v>
       </c>
       <c r="AV13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX13" t="n">
         <v>5</v>
@@ -2810,10 +2877,10 @@
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC13" t="n">
         <v>24</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -2845,46 +2912,46 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E14" t="n">
         <v>27</v>
       </c>
       <c r="F14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G14" t="n">
-        <v>0.643</v>
+        <v>0.659</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="J14" t="n">
-        <v>82.09999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="K14" t="n">
         <v>0.474</v>
       </c>
       <c r="L14" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M14" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.366</v>
+        <v>0.367</v>
       </c>
       <c r="O14" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="P14" t="n">
-        <v>29.4</v>
+        <v>29.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.752</v>
+        <v>0.755</v>
       </c>
       <c r="R14" t="n">
         <v>11</v>
@@ -2893,16 +2960,16 @@
         <v>34</v>
       </c>
       <c r="T14" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="U14" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="V14" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="W14" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X14" t="n">
         <v>5</v>
@@ -2911,25 +2978,25 @@
         <v>4.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>107</v>
+        <v>107.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG14" t="n">
         <v>7</v>
@@ -2956,13 +3023,13 @@
         <v>9</v>
       </c>
       <c r="AO14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
         <v>19</v>
@@ -2977,19 +3044,19 @@
         <v>5</v>
       </c>
       <c r="AV14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW14" t="n">
         <v>5</v>
       </c>
       <c r="AX14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AY14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA14" t="n">
         <v>6</v>
@@ -2998,7 +3065,7 @@
         <v>3</v>
       </c>
       <c r="BC14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-4.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3123,7 +3190,7 @@
         <v>8</v>
       </c>
       <c r="AJ15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK15" t="n">
         <v>7</v>
@@ -3150,7 +3217,7 @@
         <v>23</v>
       </c>
       <c r="AS15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AT15" t="n">
         <v>18</v>
@@ -3159,7 +3226,7 @@
         <v>21</v>
       </c>
       <c r="AV15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW15" t="n">
         <v>29</v>
@@ -3168,13 +3235,13 @@
         <v>7</v>
       </c>
       <c r="AY15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ15" t="n">
         <v>4</v>
       </c>
       <c r="BA15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB15" t="n">
         <v>8</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-6.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE16" t="n">
         <v>28</v>
@@ -3299,7 +3366,7 @@
         <v>28</v>
       </c>
       <c r="AH16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI16" t="n">
         <v>26</v>
@@ -3317,7 +3384,7 @@
         <v>25</v>
       </c>
       <c r="AN16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="n">
         <v>18</v>
@@ -3356,13 +3423,13 @@
         <v>11</v>
       </c>
       <c r="BA16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB16" t="n">
         <v>30</v>
       </c>
       <c r="BC16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -3391,37 +3458,37 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F17" t="n">
         <v>27</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4</v>
+        <v>0.386</v>
       </c>
       <c r="H17" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I17" t="n">
         <v>36.3</v>
       </c>
       <c r="J17" t="n">
-        <v>80.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="K17" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L17" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M17" t="n">
         <v>16.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.34</v>
+        <v>0.335</v>
       </c>
       <c r="O17" t="n">
         <v>16.8</v>
@@ -3433,115 +3500,115 @@
         <v>0.74</v>
       </c>
       <c r="R17" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="S17" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="T17" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="U17" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="V17" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W17" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y17" t="n">
         <v>5.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AA17" t="n">
         <v>20.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>95.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>-6</v>
+        <v>-6.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF17" t="n">
         <v>22</v>
       </c>
       <c r="AG17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH17" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AI17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ17" t="n">
         <v>16</v>
       </c>
       <c r="AK17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM17" t="n">
         <v>21</v>
       </c>
       <c r="AN17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO17" t="n">
         <v>25</v>
       </c>
       <c r="AP17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ17" t="n">
         <v>21</v>
       </c>
       <c r="AR17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS17" t="n">
         <v>30</v>
       </c>
       <c r="AT17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU17" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AV17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW17" t="n">
         <v>21</v>
       </c>
       <c r="AX17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AY17" t="n">
         <v>25</v>
       </c>
       <c r="AZ17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA17" t="n">
         <v>20</v>
       </c>
       <c r="BB17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC17" t="n">
         <v>26</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -3573,91 +3640,91 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F18" t="n">
         <v>35</v>
       </c>
       <c r="G18" t="n">
-        <v>0.186</v>
+        <v>0.167</v>
       </c>
       <c r="H18" t="n">
         <v>48</v>
       </c>
       <c r="I18" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J18" t="n">
-        <v>83.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="K18" t="n">
         <v>0.441</v>
       </c>
       <c r="L18" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M18" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0.343</v>
+        <v>0.342</v>
       </c>
       <c r="O18" t="n">
-        <v>15.3</v>
+        <v>15.1</v>
       </c>
       <c r="P18" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.72</v>
+        <v>0.715</v>
       </c>
       <c r="R18" t="n">
         <v>12.5</v>
       </c>
       <c r="S18" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="T18" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="U18" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="V18" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W18" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X18" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="n">
         <v>6</v>
       </c>
       <c r="Z18" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="AA18" t="n">
         <v>18.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>94.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>-8.4</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
       </c>
       <c r="AF18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG18" t="n">
         <v>30</v>
@@ -3666,16 +3733,16 @@
         <v>29</v>
       </c>
       <c r="AI18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK18" t="n">
         <v>24</v>
       </c>
       <c r="AL18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM18" t="n">
         <v>22</v>
@@ -3684,7 +3751,7 @@
         <v>19</v>
       </c>
       <c r="AO18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP18" t="n">
         <v>28</v>
@@ -3705,10 +3772,10 @@
         <v>28</v>
       </c>
       <c r="AV18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -3755,25 +3822,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E19" t="n">
         <v>18</v>
       </c>
       <c r="F19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G19" t="n">
-        <v>0.409</v>
+        <v>0.419</v>
       </c>
       <c r="H19" t="n">
         <v>48.5</v>
       </c>
       <c r="I19" t="n">
-        <v>33.7</v>
+        <v>33.8</v>
       </c>
       <c r="J19" t="n">
-        <v>77.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="K19" t="n">
         <v>0.433</v>
@@ -3788,55 +3855,55 @@
         <v>0.333</v>
       </c>
       <c r="O19" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="P19" t="n">
-        <v>29</v>
+        <v>28.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.713</v>
+        <v>0.715</v>
       </c>
       <c r="R19" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="S19" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T19" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U19" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="V19" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W19" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X19" t="n">
         <v>4.7</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z19" t="n">
         <v>23</v>
       </c>
       <c r="AA19" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="AB19" t="n">
         <v>93.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>-6.2</v>
+        <v>-6.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF19" t="n">
         <v>19</v>
@@ -3845,7 +3912,7 @@
         <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3863,7 +3930,7 @@
         <v>17</v>
       </c>
       <c r="AN19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO19" t="n">
         <v>10</v>
@@ -3872,16 +3939,16 @@
         <v>5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AU19" t="n">
         <v>4</v>
@@ -3896,13 +3963,13 @@
         <v>16</v>
       </c>
       <c r="AY19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ19" t="n">
         <v>26</v>
       </c>
       <c r="BA19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB19" t="n">
         <v>28</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -4015,10 +4082,10 @@
         <v>6.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="n">
         <v>2</v>
@@ -4027,16 +4094,16 @@
         <v>2</v>
       </c>
       <c r="AH20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI20" t="n">
         <v>7</v>
       </c>
       <c r="AJ20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL20" t="n">
         <v>7</v>
@@ -4048,7 +4115,7 @@
         <v>4</v>
       </c>
       <c r="AO20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP20" t="n">
         <v>30</v>
@@ -4072,13 +4139,13 @@
         <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX20" t="n">
         <v>27</v>
       </c>
       <c r="AY20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ20" t="n">
         <v>2</v>
@@ -4087,7 +4154,7 @@
         <v>28</v>
       </c>
       <c r="BB20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC20" t="n">
         <v>3</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -4119,58 +4186,58 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E21" t="n">
         <v>14</v>
       </c>
       <c r="F21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G21" t="n">
-        <v>0.326</v>
+        <v>0.333</v>
       </c>
       <c r="H21" t="n">
         <v>48.2</v>
       </c>
       <c r="I21" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="J21" t="n">
-        <v>80</v>
+        <v>79.8</v>
       </c>
       <c r="K21" t="n">
         <v>0.438</v>
       </c>
       <c r="L21" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="M21" t="n">
         <v>17</v>
       </c>
       <c r="N21" t="n">
-        <v>0.33</v>
+        <v>0.333</v>
       </c>
       <c r="O21" t="n">
         <v>18.8</v>
       </c>
       <c r="P21" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.715</v>
+        <v>0.713</v>
       </c>
       <c r="R21" t="n">
         <v>12.5</v>
       </c>
       <c r="S21" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="T21" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="U21" t="n">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="V21" t="n">
         <v>15.4</v>
@@ -4179,31 +4246,31 @@
         <v>6.3</v>
       </c>
       <c r="X21" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>94.5</v>
+        <v>94.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>-5.9</v>
+        <v>-6</v>
       </c>
       <c r="AD21" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AE21" t="n">
         <v>25</v>
       </c>
       <c r="AF21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG21" t="n">
         <v>25</v>
@@ -4218,31 +4285,31 @@
         <v>18</v>
       </c>
       <c r="AK21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AM21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO21" t="n">
         <v>14</v>
       </c>
       <c r="AP21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR21" t="n">
         <v>4</v>
       </c>
       <c r="AS21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT21" t="n">
         <v>17</v>
@@ -4260,16 +4327,16 @@
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA21" t="n">
         <v>15</v>
       </c>
       <c r="BB21" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BC21" t="n">
         <v>25</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F22" t="n">
         <v>18</v>
       </c>
       <c r="G22" t="n">
-        <v>0.609</v>
+        <v>0.6</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4319,7 +4386,7 @@
         <v>36.6</v>
       </c>
       <c r="J22" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="K22" t="n">
         <v>0.465</v>
@@ -4331,40 +4398,40 @@
         <v>24.8</v>
       </c>
       <c r="N22" t="n">
-        <v>0.363</v>
+        <v>0.364</v>
       </c>
       <c r="O22" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="P22" t="n">
-        <v>29.2</v>
+        <v>29.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.722</v>
+        <v>0.718</v>
       </c>
       <c r="R22" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="S22" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="T22" t="n">
         <v>42.4</v>
       </c>
       <c r="U22" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V22" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W22" t="n">
         <v>6.5</v>
       </c>
       <c r="X22" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z22" t="n">
         <v>21.1</v>
@@ -4373,7 +4440,7 @@
         <v>24.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>103.2</v>
+        <v>103.4</v>
       </c>
       <c r="AC22" t="n">
         <v>3.2</v>
@@ -4382,16 +4449,16 @@
         <v>1</v>
       </c>
       <c r="AE22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF22" t="n">
         <v>9</v>
       </c>
       <c r="AG22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH22" t="n">
         <v>8</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>10</v>
       </c>
       <c r="AI22" t="n">
         <v>14</v>
@@ -4415,13 +4482,13 @@
         <v>7</v>
       </c>
       <c r="AP22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS22" t="n">
         <v>5</v>
@@ -4433,16 +4500,16 @@
         <v>23</v>
       </c>
       <c r="AV22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW22" t="n">
         <v>26</v>
       </c>
       <c r="AX22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AZ22" t="n">
         <v>13</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -4561,10 +4628,10 @@
         <v>-3</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF23" t="n">
         <v>25</v>
@@ -4594,7 +4661,7 @@
         <v>30</v>
       </c>
       <c r="AO23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP23" t="n">
         <v>14</v>
@@ -4615,19 +4682,19 @@
         <v>27</v>
       </c>
       <c r="AV23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW23" t="n">
         <v>6</v>
       </c>
       <c r="AX23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA23" t="n">
         <v>19</v>
@@ -4636,7 +4703,7 @@
         <v>29</v>
       </c>
       <c r="BC23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -4665,61 +4732,61 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E24" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F24" t="n">
         <v>13</v>
       </c>
       <c r="G24" t="n">
-        <v>0.711</v>
+        <v>0.705</v>
       </c>
       <c r="H24" t="n">
         <v>48.1</v>
       </c>
       <c r="I24" t="n">
-        <v>41.4</v>
+        <v>41.6</v>
       </c>
       <c r="J24" t="n">
-        <v>84.40000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.491</v>
+        <v>0.492</v>
       </c>
       <c r="L24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M24" t="n">
         <v>23.7</v>
       </c>
       <c r="N24" t="n">
-        <v>0.386</v>
+        <v>0.39</v>
       </c>
       <c r="O24" t="n">
         <v>17.5</v>
       </c>
       <c r="P24" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.787</v>
+        <v>0.784</v>
       </c>
       <c r="R24" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="S24" t="n">
         <v>32.2</v>
       </c>
       <c r="T24" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="U24" t="n">
-        <v>27.5</v>
+        <v>27.7</v>
       </c>
       <c r="V24" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="W24" t="n">
         <v>7.3</v>
@@ -4728,22 +4795,22 @@
         <v>6.9</v>
       </c>
       <c r="Y24" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AA24" t="n">
         <v>19.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>109.5</v>
+        <v>110</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
@@ -4755,7 +4822,7 @@
         <v>3</v>
       </c>
       <c r="AH24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI24" t="n">
         <v>1</v>
@@ -4776,7 +4843,7 @@
         <v>3</v>
       </c>
       <c r="AO24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP24" t="n">
         <v>27</v>
@@ -4800,7 +4867,7 @@
         <v>6</v>
       </c>
       <c r="AW24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AX24" t="n">
         <v>2</v>
@@ -4812,13 +4879,13 @@
         <v>3</v>
       </c>
       <c r="BA24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB24" t="n">
         <v>1</v>
       </c>
       <c r="BC24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F25" t="n">
         <v>18</v>
       </c>
       <c r="G25" t="n">
-        <v>0.591</v>
+        <v>0.581</v>
       </c>
       <c r="H25" t="n">
         <v>48.7</v>
@@ -4865,70 +4932,70 @@
         <v>35.8</v>
       </c>
       <c r="J25" t="n">
-        <v>78.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="K25" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L25" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M25" t="n">
         <v>17.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.395</v>
+        <v>0.397</v>
       </c>
       <c r="O25" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="P25" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.768</v>
+        <v>0.766</v>
       </c>
       <c r="R25" t="n">
         <v>10.4</v>
       </c>
       <c r="S25" t="n">
-        <v>29.7</v>
+        <v>29.9</v>
       </c>
       <c r="T25" t="n">
-        <v>40.1</v>
+        <v>40.3</v>
       </c>
       <c r="U25" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V25" t="n">
         <v>13.7</v>
       </c>
       <c r="W25" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="X25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y25" t="n">
         <v>3.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>96.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC25" t="n">
         <v>0.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF25" t="n">
         <v>9</v>
@@ -4940,13 +5007,13 @@
         <v>2</v>
       </c>
       <c r="AI25" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AJ25" t="n">
         <v>24</v>
       </c>
       <c r="AK25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL25" t="n">
         <v>11</v>
@@ -4958,10 +5025,10 @@
         <v>2</v>
       </c>
       <c r="AO25" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AP25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ25" t="n">
         <v>9</v>
@@ -4976,10 +5043,10 @@
         <v>28</v>
       </c>
       <c r="AU25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW25" t="n">
         <v>30</v>
@@ -4991,10 +5058,10 @@
         <v>4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB25" t="n">
         <v>19</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F26" t="n">
         <v>24</v>
       </c>
       <c r="G26" t="n">
-        <v>0.442</v>
+        <v>0.429</v>
       </c>
       <c r="H26" t="n">
         <v>48.2</v>
@@ -5068,19 +5135,19 @@
         <v>27.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.796</v>
+        <v>0.794</v>
       </c>
       <c r="R26" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S26" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="T26" t="n">
         <v>39.2</v>
       </c>
       <c r="U26" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="V26" t="n">
         <v>16.6</v>
@@ -5089,28 +5156,28 @@
         <v>8</v>
       </c>
       <c r="X26" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Y26" t="n">
         <v>5.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="AA26" t="n">
         <v>23.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.7</v>
+        <v>-2.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AE26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AF26" t="n">
         <v>18</v>
@@ -5122,7 +5189,7 @@
         <v>19</v>
       </c>
       <c r="AI26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ26" t="n">
         <v>27</v>
@@ -5140,19 +5207,19 @@
         <v>8</v>
       </c>
       <c r="AO26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ26" t="n">
         <v>4</v>
       </c>
-      <c r="AP26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>3</v>
-      </c>
       <c r="AR26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS26" t="n">
         <v>25</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>24</v>
       </c>
       <c r="AT26" t="n">
         <v>29</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>5</v>
       </c>
       <c r="AD27" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AE27" t="n">
         <v>6</v>
@@ -5301,7 +5368,7 @@
         <v>6</v>
       </c>
       <c r="AH27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI27" t="n">
         <v>19</v>
@@ -5328,7 +5395,7 @@
         <v>26</v>
       </c>
       <c r="AQ27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR27" t="n">
         <v>22</v>
@@ -5358,10 +5425,10 @@
         <v>1</v>
       </c>
       <c r="BA27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC27" t="n">
         <v>7</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -5393,25 +5460,25 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E28" t="n">
         <v>9</v>
       </c>
       <c r="F28" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G28" t="n">
-        <v>0.205</v>
+        <v>0.209</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
       </c>
       <c r="I28" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="J28" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="K28" t="n">
         <v>0.436</v>
@@ -5426,16 +5493,16 @@
         <v>0.333</v>
       </c>
       <c r="O28" t="n">
-        <v>17.8</v>
+        <v>17.5</v>
       </c>
       <c r="P28" t="n">
-        <v>23.3</v>
+        <v>22.9</v>
       </c>
       <c r="Q28" t="n">
         <v>0.765</v>
       </c>
       <c r="R28" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S28" t="n">
         <v>33.4</v>
@@ -5444,46 +5511,46 @@
         <v>45.1</v>
       </c>
       <c r="U28" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="V28" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="W28" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="X28" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB28" t="n">
-        <v>96.8</v>
+        <v>96.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>-8.199999999999999</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="AD28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE28" t="n">
         <v>28</v>
       </c>
       <c r="AF28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AH28" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AI28" t="n">
         <v>9</v>
@@ -5501,19 +5568,19 @@
         <v>27</v>
       </c>
       <c r="AN28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO28" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS28" t="n">
         <v>2</v>
@@ -5525,10 +5592,10 @@
         <v>19</v>
       </c>
       <c r="AV28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX28" t="n">
         <v>8</v>
@@ -5543,7 +5610,7 @@
         <v>24</v>
       </c>
       <c r="BB28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC28" t="n">
         <v>29</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -5653,19 +5720,19 @@
         <v>2.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE29" t="n">
         <v>13</v>
       </c>
       <c r="AF29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI29" t="n">
         <v>10</v>
@@ -5695,7 +5762,7 @@
         <v>2</v>
       </c>
       <c r="AR29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS29" t="n">
         <v>15</v>
@@ -5716,7 +5783,7 @@
         <v>25</v>
       </c>
       <c r="AY29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ29" t="n">
         <v>7</v>
@@ -5728,7 +5795,7 @@
         <v>14</v>
       </c>
       <c r="BC29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -5757,25 +5824,25 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F30" t="n">
         <v>18</v>
       </c>
       <c r="G30" t="n">
-        <v>0.591</v>
+        <v>0.581</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>39.7</v>
+        <v>39.8</v>
       </c>
       <c r="J30" t="n">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="K30" t="n">
         <v>0.493</v>
@@ -5787,22 +5854,22 @@
         <v>11.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0.361</v>
+        <v>0.36</v>
       </c>
       <c r="O30" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="P30" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.752</v>
+        <v>0.749</v>
       </c>
       <c r="R30" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S30" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="T30" t="n">
         <v>40.7</v>
@@ -5811,10 +5878,10 @@
         <v>26</v>
       </c>
       <c r="V30" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W30" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="X30" t="n">
         <v>4.3</v>
@@ -5823,22 +5890,22 @@
         <v>6</v>
       </c>
       <c r="Z30" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>105.5</v>
+        <v>105.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF30" t="n">
         <v>9</v>
@@ -5853,7 +5920,7 @@
         <v>3</v>
       </c>
       <c r="AJ30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK30" t="n">
         <v>1</v>
@@ -5865,19 +5932,19 @@
         <v>30</v>
       </c>
       <c r="AN30" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP30" t="n">
         <v>3</v>
       </c>
-      <c r="AP30" t="n">
-        <v>4</v>
-      </c>
       <c r="AQ30" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AR30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS30" t="n">
         <v>28</v>
@@ -5889,7 +5956,7 @@
         <v>2</v>
       </c>
       <c r="AV30" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AW30" t="n">
         <v>3</v>
@@ -5904,7 +5971,7 @@
         <v>30</v>
       </c>
       <c r="BA30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB30" t="n">
         <v>5</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
@@ -5939,40 +6006,40 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E31" t="n">
         <v>23</v>
       </c>
       <c r="F31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G31" t="n">
-        <v>0.548</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I31" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J31" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L31" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M31" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="N31" t="n">
-        <v>0.347</v>
+        <v>0.344</v>
       </c>
       <c r="O31" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="P31" t="n">
         <v>24.2</v>
@@ -5984,7 +6051,7 @@
         <v>12</v>
       </c>
       <c r="S31" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="T31" t="n">
         <v>42.5</v>
@@ -6002,7 +6069,7 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z31" t="n">
         <v>19.6</v>
@@ -6011,28 +6078,28 @@
         <v>19.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>99.2</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG31" t="n">
         <v>13</v>
       </c>
-      <c r="AG31" t="n">
-        <v>15</v>
-      </c>
       <c r="AH31" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AI31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ31" t="n">
         <v>11</v>
@@ -6041,7 +6108,7 @@
         <v>18</v>
       </c>
       <c r="AL31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM31" t="n">
         <v>11</v>
@@ -6050,16 +6117,16 @@
         <v>18</v>
       </c>
       <c r="AO31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP31" t="n">
         <v>19</v>
       </c>
       <c r="AQ31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS31" t="n">
         <v>16</v>
@@ -6074,13 +6141,13 @@
         <v>9</v>
       </c>
       <c r="AW31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ31" t="n">
         <v>5</v>
@@ -6092,7 +6159,7 @@
         <v>11</v>
       </c>
       <c r="BC31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-27-2007-08</t>
+          <t>2008-01-27</t>
         </is>
       </c>
     </row>
